--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B7" t="n">
-        <v>91210</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R7" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>91284</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R8" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>91290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R7" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>91284</v>
+        <v>57761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R8" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>91291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R5" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91290</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R6" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128089</v>
+        <v>127128091</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>98464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777398</v>
+        <v>777416</v>
       </c>
       <c r="R2" t="n">
-        <v>7132328</v>
+        <v>7132174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128091</v>
+        <v>127128089</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>91326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777416</v>
+        <v>777398</v>
       </c>
       <c r="R3" t="n">
-        <v>7132174</v>
+        <v>7132328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R5" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>91291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R6" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91326</v>
+        <v>91291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R5" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R6" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B7" t="n">
-        <v>91291</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R7" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>91291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R8" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128091</v>
+        <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>98464</v>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777416</v>
+        <v>777398</v>
       </c>
       <c r="R2" t="n">
-        <v>7132174</v>
+        <v>7132328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128089</v>
+        <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>91326</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777398</v>
+        <v>777416</v>
       </c>
       <c r="R3" t="n">
-        <v>7132328</v>
+        <v>7132174</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91291</v>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R5" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>91295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R6" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>91295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R7" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>57765</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R8" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91330</v>
+        <v>91295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R5" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91295</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R6" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128089</v>
+        <v>127128091</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777398</v>
+        <v>777416</v>
       </c>
       <c r="R2" t="n">
-        <v>7132328</v>
+        <v>7132174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128091</v>
+        <v>127128089</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777416</v>
+        <v>777398</v>
       </c>
       <c r="R3" t="n">
-        <v>7132174</v>
+        <v>7132328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128091</v>
+        <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777416</v>
+        <v>777398</v>
       </c>
       <c r="R2" t="n">
-        <v>7132174</v>
+        <v>7132328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128089</v>
+        <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777398</v>
+        <v>777416</v>
       </c>
       <c r="R3" t="n">
-        <v>7132328</v>
+        <v>7132174</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B7" t="n">
-        <v>91295</v>
+        <v>57765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R7" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B8" t="n">
-        <v>57765</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R8" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128089</v>
+        <v>127128091</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777398</v>
+        <v>777416</v>
       </c>
       <c r="R2" t="n">
-        <v>7132328</v>
+        <v>7132174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128091</v>
+        <v>127128089</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777416</v>
+        <v>777398</v>
       </c>
       <c r="R3" t="n">
-        <v>7132174</v>
+        <v>7132328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128091</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128089</v>
       </c>
       <c r="B3" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>91332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R5" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91330</v>
+        <v>91297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R6" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127128092</v>
       </c>
       <c r="B7" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>127128084</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127128091</v>
+        <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>98471</v>
+        <v>91332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777416</v>
+        <v>777398</v>
       </c>
       <c r="R2" t="n">
-        <v>7132174</v>
+        <v>7132328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127128089</v>
+        <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>91332</v>
+        <v>98471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777398</v>
+        <v>777416</v>
       </c>
       <c r="R3" t="n">
-        <v>7132328</v>
+        <v>7132174</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91332</v>
+        <v>91297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R5" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91297</v>
+        <v>91332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R6" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>57767</v>
+        <v>91297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R7" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>57767</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R8" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91303</v>
+        <v>91341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R5" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91338</v>
+        <v>91306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R6" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B7" t="n">
-        <v>91303</v>
+        <v>57770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R7" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B8" t="n">
-        <v>57767</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,42 +1276,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R8" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91341</v>
+        <v>91314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R5" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91306</v>
+        <v>91349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R6" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>57770</v>
+        <v>91314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R7" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>57776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1268,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R8" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98488</v>
+        <v>98653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91314</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91314</v>
+        <v>91469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91349</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91314</v>
+        <v>91469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>57776</v>
+        <v>57820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1382,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127128089</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127128091</v>
       </c>
       <c r="B3" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127128085</v>
       </c>
       <c r="B4" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B5" t="n">
-        <v>91513</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R5" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R6" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B7" t="n">
-        <v>91513</v>
+        <v>57831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1191,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R7" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B8" t="n">
-        <v>57831</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,42 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R8" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 34723-2025 artfynd.xlsx
+++ b/artfynd/A 34723-2025 artfynd.xlsx
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127128088</v>
+        <v>127128086</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777414</v>
+        <v>777434</v>
       </c>
       <c r="R5" t="n">
-        <v>7132376</v>
+        <v>7132345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127128086</v>
+        <v>127128088</v>
       </c>
       <c r="B6" t="n">
-        <v>91513</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777434</v>
+        <v>777414</v>
       </c>
       <c r="R6" t="n">
-        <v>7132345</v>
+        <v>7132376</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127128092</v>
+        <v>127128084</v>
       </c>
       <c r="B7" t="n">
-        <v>57831</v>
+        <v>91513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777430</v>
+        <v>777371</v>
       </c>
       <c r="R7" t="n">
-        <v>7132432</v>
+        <v>7132052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127128084</v>
+        <v>127128092</v>
       </c>
       <c r="B8" t="n">
-        <v>91513</v>
+        <v>57831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,34 +1292,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hökmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777371</v>
+        <v>777430</v>
       </c>
       <c r="R8" t="n">
-        <v>7132052</v>
+        <v>7132432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
